--- a/output/Data and Chart Outputs/trinidad_gas.xlsx
+++ b/output/Data and Chart Outputs/trinidad_gas.xlsx
@@ -157,7 +157,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Trinidad &amp; Tobago gas use by sector (to May/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Trinidad &amp; Tobago gas use by sector (to Jun/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -187,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$66</f>
+              <f>'Chart'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$66</f>
+              <f>'Chart'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -215,12 +216,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$66</f>
+              <f>'Chart'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$66</f>
+              <f>'Chart'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$66</f>
+              <f>'Chart'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$66</f>
+              <f>'Chart'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -271,12 +272,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$66</f>
+              <f>'Chart'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$66</f>
+              <f>'Chart'!$E$2:$E$67</f>
             </numRef>
           </val>
         </ser>
@@ -299,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$66</f>
+              <f>'Chart'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$66</f>
+              <f>'Chart'!$F$2:$F$67</f>
             </numRef>
           </val>
         </ser>
@@ -404,7 +405,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Trinidad &amp; Tobago gas production by company (to May/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Trinidad &amp; Tobago gas production by company (to Jun/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -434,12 +436,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$66</f>
+              <f>'Chart - Production'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$B$2:$B$66</f>
+              <f>'Chart - Production'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -462,12 +464,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$66</f>
+              <f>'Chart - Production'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$C$2:$C$66</f>
+              <f>'Chart - Production'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -490,12 +492,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$66</f>
+              <f>'Chart - Production'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$D$2:$D$66</f>
+              <f>'Chart - Production'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -518,12 +520,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$66</f>
+              <f>'Chart - Production'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$E$2:$E$66</f>
+              <f>'Chart - Production'!$E$2:$E$67</f>
             </numRef>
           </val>
         </ser>
@@ -546,12 +548,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$66</f>
+              <f>'Chart - Production'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$F$2:$F$66</f>
+              <f>'Chart - Production'!$F$2:$F$67</f>
             </numRef>
           </val>
         </ser>
@@ -574,12 +576,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$66</f>
+              <f>'Chart - Production'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$G$2:$G$66</f>
+              <f>'Chart - Production'!$G$2:$G$67</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +604,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$66</f>
+              <f>'Chart - Production'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$H$2:$H$66</f>
+              <f>'Chart - Production'!$H$2:$H$67</f>
             </numRef>
           </val>
         </ser>
@@ -630,12 +632,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$66</f>
+              <f>'Chart - Production'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$I$2:$I$66</f>
+              <f>'Chart - Production'!$I$2:$I$67</f>
             </numRef>
           </val>
         </ser>
@@ -1164,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1219,7 +1221,7 @@
         <v>243.2176451612903</v>
       </c>
       <c r="F2" t="n">
-        <v>98.87292893548465</v>
+        <v>98.8729289354842</v>
       </c>
     </row>
     <row r="3">
@@ -1439,7 +1441,7 @@
         <v>246.6372258064517</v>
       </c>
       <c r="F13" t="n">
-        <v>90.19469892473171</v>
+        <v>90.19469892473126</v>
       </c>
     </row>
     <row r="14">
@@ -1459,7 +1461,7 @@
         <v>227.9308387096774</v>
       </c>
       <c r="F14" t="n">
-        <v>88.95189964516112</v>
+        <v>88.95189964516157</v>
       </c>
     </row>
     <row r="15">
@@ -1499,7 +1501,7 @@
         <v>261.5239677419355</v>
       </c>
       <c r="F16" t="n">
-        <v>82.72002116129033</v>
+        <v>82.72002116129079</v>
       </c>
     </row>
     <row r="17">
@@ -1539,7 +1541,7 @@
         <v>282.2281935483871</v>
       </c>
       <c r="F18" t="n">
-        <v>76.07614609677375</v>
+        <v>76.07614609677421</v>
       </c>
     </row>
     <row r="19">
@@ -1579,7 +1581,7 @@
         <v>302.9440322580645</v>
       </c>
       <c r="F20" t="n">
-        <v>100.6291136451614</v>
+        <v>100.6291136451619</v>
       </c>
     </row>
     <row r="21">
@@ -1619,7 +1621,7 @@
         <v>265.8368</v>
       </c>
       <c r="F22" t="n">
-        <v>97.38659396666662</v>
+        <v>97.38659396666708</v>
       </c>
     </row>
     <row r="23">
@@ -1779,7 +1781,7 @@
         <v>264.4945483870968</v>
       </c>
       <c r="F30" t="n">
-        <v>79.1975824193546</v>
+        <v>79.19758241935506</v>
       </c>
     </row>
     <row r="31">
@@ -1879,7 +1881,7 @@
         <v>261.242451612903</v>
       </c>
       <c r="F35" t="n">
-        <v>41.74717170967733</v>
+        <v>41.74717170967779</v>
       </c>
     </row>
     <row r="36">
@@ -2059,7 +2061,7 @@
         <v>283.6095489677419</v>
       </c>
       <c r="F44" t="n">
-        <v>89.50409167741964</v>
+        <v>89.50409167741918</v>
       </c>
     </row>
     <row r="45">
@@ -2199,7 +2201,7 @@
         <v>244.38</v>
       </c>
       <c r="F51" t="n">
-        <v>87.8700000000008</v>
+        <v>87.87000000000035</v>
       </c>
     </row>
     <row r="52">
@@ -2239,7 +2241,7 @@
         <v>258.7987916666667</v>
       </c>
       <c r="F53" t="n">
-        <v>88.94767700000011</v>
+        <v>88.94767699999966</v>
       </c>
     </row>
     <row r="54">
@@ -2259,7 +2261,7 @@
         <v>279.0247813225806</v>
       </c>
       <c r="F54" t="n">
-        <v>84.27533838709633</v>
+        <v>84.27533838709678</v>
       </c>
     </row>
     <row r="55">
@@ -2319,7 +2321,7 @@
         <v>266.2585112580649</v>
       </c>
       <c r="F57" t="n">
-        <v>90.6386588709679</v>
+        <v>90.63865887096745</v>
       </c>
     </row>
     <row r="58">
@@ -2439,7 +2441,7 @@
         <v>238.1228512142857</v>
       </c>
       <c r="F63" t="n">
-        <v>87.78491825000037</v>
+        <v>87.78491824999992</v>
       </c>
     </row>
     <row r="64">
@@ -2500,6 +2502,26 @@
       </c>
       <c r="F66" t="n">
         <v>88.49671762365597</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>922.048178</v>
+      </c>
+      <c r="C67" t="n">
+        <v>455.0398015333333</v>
+      </c>
+      <c r="D67" t="n">
+        <v>340.7869332333333</v>
+      </c>
+      <c r="E67" t="n">
+        <v>269.0721754</v>
+      </c>
+      <c r="F67" t="n">
+        <v>81.87889816666666</v>
       </c>
     </row>
   </sheetData>
@@ -2514,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4191,6 +4213,32 @@
         <v>21.85129032258065</v>
       </c>
       <c r="I66" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>797.3863936666667</v>
+      </c>
+      <c r="C67" t="n">
+        <v>387.4246</v>
+      </c>
+      <c r="D67" t="n">
+        <v>417.1952573337</v>
+      </c>
+      <c r="E67" t="n">
+        <v>534.181</v>
+      </c>
+      <c r="G67" t="n">
+        <v>25.59587312101685</v>
+      </c>
+      <c r="H67" t="n">
+        <v>13.27866666666667</v>
+      </c>
+      <c r="I67" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4206,7 +4254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F619"/>
+  <dimension ref="A1:F628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19156,7 +19204,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19230,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19208,7 +19256,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19282,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19260,7 +19308,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19286,7 +19334,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19360,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19386,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19364,7 +19412,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19438,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19416,7 +19464,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19442,7 +19490,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19468,7 +19516,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19542,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19520,7 +19568,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19594,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19572,7 +19620,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19598,7 +19646,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19624,7 +19672,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19650,7 +19698,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19676,7 +19724,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19750,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19728,7 +19776,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19802,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19828,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19806,7 +19854,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19832,7 +19880,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19858,7 +19906,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19932,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19910,7 +19958,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19936,7 +19984,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19962,7 +20010,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -19988,7 +20036,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20014,7 +20062,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20040,7 +20088,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20066,7 +20114,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20092,7 +20140,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20118,7 +20166,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20144,7 +20192,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20218,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20196,7 +20244,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20270,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20248,7 +20296,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20322,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20300,7 +20348,241 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>618</v>
+      </c>
+      <c r="B620" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>797.3863936666667</v>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>619</v>
+      </c>
+      <c r="B621" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>534.181</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>620</v>
+      </c>
+      <c r="B622" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>2</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>621</v>
+      </c>
+      <c r="B623" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>14</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>622</v>
+      </c>
+      <c r="B624" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>417.1952573337</v>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>623</v>
+      </c>
+      <c r="B625" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>13.27866666666667</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>624</v>
+      </c>
+      <c r="B626" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>387.4246</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>625</v>
+      </c>
+      <c r="B627" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>2191.06179078805</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>626</v>
+      </c>
+      <c r="B628" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>25.59587312101685</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F692"/>
+  <dimension ref="A1:F703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36903,7 +37185,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -36929,7 +37211,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -36955,7 +37237,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -36981,7 +37263,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37007,7 +37289,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37033,7 +37315,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37059,7 +37341,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37085,7 +37367,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37111,7 +37393,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37137,7 +37419,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37163,7 +37445,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37189,7 +37471,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37215,7 +37497,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37523,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37267,7 +37549,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37293,7 +37575,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37319,7 +37601,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37345,7 +37627,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37371,7 +37653,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37397,7 +37679,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37423,7 +37705,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37449,7 +37731,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37475,7 +37757,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37501,7 +37783,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37527,7 +37809,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37553,7 +37835,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37579,7 +37861,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37605,7 +37887,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37631,7 +37913,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37657,7 +37939,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37683,7 +37965,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37709,7 +37991,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37735,7 +38017,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37761,7 +38043,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37787,7 +38069,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37813,7 +38095,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37839,7 +38121,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37865,7 +38147,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37891,7 +38173,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37917,7 +38199,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37943,7 +38225,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37969,7 +38251,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -37995,7 +38277,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38021,7 +38303,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38047,7 +38329,7 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38073,7 +38355,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38099,7 +38381,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38125,7 +38407,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38151,7 +38433,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38459,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38203,7 +38485,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38511,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38255,7 +38537,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38281,7 +38563,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -38307,7 +38589,293 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>691</v>
+      </c>
+      <c r="B693" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>6.784761333333333</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>692</v>
+      </c>
+      <c r="B694" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>334.0021719</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>693</v>
+      </c>
+      <c r="B695" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>11.67995336666667</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>694</v>
+      </c>
+      <c r="B696" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>16.38017866666667</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>695</v>
+      </c>
+      <c r="B697" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>44.35195573333333</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>696</v>
+      </c>
+      <c r="B698" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>922.048178</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>697</v>
+      </c>
+      <c r="B699" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>455.0398015333333</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>698</v>
+      </c>
+      <c r="B700" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>1.2253</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>699</v>
+      </c>
+      <c r="B701" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>269.0721754</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>700</v>
+      </c>
+      <c r="B702" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>8.241510400000001</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>701</v>
+      </c>
+      <c r="B703" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>2068.825986333333</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/10/MEEI-Consolidated-Monthly-Bulletins_January-June-2026-16-10-2026.xlsx</t>
         </is>
       </c>
     </row>
